--- a/BASE/esp32-c6_pin_definitions.xlsx
+++ b/BASE/esp32-c6_pin_definitions.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="88">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -178,13 +178,16 @@
     <t xml:space="preserve">GPIO9, chip boot mode</t>
   </si>
   <si>
+    <t xml:space="preserve">GPIO_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IO18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPIO18, SDIO_CMD, FSPICS2</t>
+  </si>
+  <si>
     <t xml:space="preserve">GPIO_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IO18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPIO18, SDIO_CMD, FSPICS2</t>
   </si>
   <si>
     <t xml:space="preserve">IO19</t>
@@ -1165,7 +1168,7 @@
         <v>54</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H17" s="4" t="str">
         <f aca="false">E12</f>
@@ -1185,7 +1188,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>17</v>
@@ -1194,10 +1197,10 @@
         <v>14</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H18" s="4" t="str">
         <f aca="false">E13</f>
@@ -1217,7 +1220,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>18</v>
@@ -1226,10 +1229,10 @@
         <v>14</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H19" s="4" t="str">
         <f aca="false">E14</f>
@@ -1249,7 +1252,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>19</v>
@@ -1258,10 +1261,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="4" t="str">
         <f aca="false">E15</f>
@@ -1276,12 +1279,12 @@
       </c>
       <c r="L20" s="4" t="str">
         <f aca="false">E16</f>
-        <v>GPIO_8</v>
+        <v>GPIO_7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>20</v>
@@ -1290,15 +1293,15 @@
         <v>14</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>21</v>
@@ -1307,10 +1310,10 @@
         <v>14</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1321,7 +1324,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>43</v>
@@ -1332,7 +1335,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>23</v>
@@ -1341,15 +1344,15 @@
         <v>14</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>24</v>
@@ -1358,15 +1361,15 @@
         <v>14</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>25</v>
@@ -1375,15 +1378,15 @@
         <v>14</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>26</v>
@@ -1392,15 +1395,15 @@
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>27</v>
@@ -1409,10 +1412,10 @@
         <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1434,7 +1437,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>29</v>
